--- a/artfynd/A 62079-2025 artfynd.xlsx
+++ b/artfynd/A 62079-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126402083</v>
+        <v>126402079</v>
       </c>
       <c r="B2" t="n">
-        <v>55441</v>
+        <v>56338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206063</v>
+        <v>100127</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ål</t>
+          <t>Öring</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anguilla anguilla</t>
+          <t>Salmo trutta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126402625</v>
+        <v>126402251</v>
       </c>
       <c r="B3" t="n">
-        <v>55441</v>
+        <v>56338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206063</v>
+        <v>100127</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ål</t>
+          <t>Öring</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anguilla anguilla</t>
+          <t>Salmo trutta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1994-09-05</t>
+          <t>1992-08-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1994-09-05</t>
+          <t>1992-08-24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -876,6 +876,210 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126402083</v>
+      </c>
+      <c r="B4" t="n">
+        <v>55724</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>206063</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Anguilla anguilla</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gärån, Härsnäs, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>348769</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6383593</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sätila</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1986-09-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1986-09-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Elfiske fr Lst, gammal artuppgift, inlagd av Marks Kommun</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jenny Pleym</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Jenny Pleym</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126402625</v>
+      </c>
+      <c r="B5" t="n">
+        <v>55724</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>206063</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ål</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Anguilla anguilla</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gärån, Skogen G2, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>348471</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6383489</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mark</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sätila</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1994-09-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1994-09-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Elfiske fr Lst, gammal artuppgift, inlagd av Marks Kommun</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jenny Pleym</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Jenny Pleym</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
